--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>66</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.34e+05</t>
-  </si>
-  <si>
-    <t>(75084.004)</t>
-  </si>
-  <si>
-    <t>499.793</t>
-  </si>
-  <si>
-    <t>(36.056)</t>
-  </si>
-  <si>
-    <t>3.639</t>
-  </si>
-  <si>
-    <t>(0.050)</t>
-  </si>
-  <si>
-    <t>8.239</t>
-  </si>
-  <si>
-    <t>(1.393)</t>
-  </si>
-  <si>
-    <t>87.818</t>
-  </si>
-  <si>
-    <t>(0.501)</t>
-  </si>
-  <si>
-    <t>9.87e+05</t>
-  </si>
-  <si>
-    <t>(57883.460)</t>
-  </si>
-  <si>
-    <t>2.400</t>
-  </si>
-  <si>
-    <t>(0.140)</t>
-  </si>
-  <si>
-    <t>2.910</t>
-  </si>
-  <si>
-    <t>(0.408)</t>
-  </si>
-  <si>
-    <t>31.821</t>
-  </si>
-  <si>
-    <t>(3.927)</t>
-  </si>
-  <si>
-    <t>0.940</t>
-  </si>
-  <si>
-    <t>(0.029)</t>
-  </si>
-  <si>
-    <t>49</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.23e+05</t>
-  </si>
-  <si>
-    <t>(1.14e+05)</t>
-  </si>
-  <si>
-    <t>482.848</t>
-  </si>
-  <si>
-    <t>(48.706)</t>
-  </si>
-  <si>
-    <t>3.353</t>
-  </si>
-  <si>
-    <t>(0.051)</t>
-  </si>
-  <si>
-    <t>26.673</t>
-  </si>
-  <si>
-    <t>(3.766)</t>
-  </si>
-  <si>
-    <t>91.408</t>
-  </si>
-  <si>
-    <t>(0.410)</t>
-  </si>
-  <si>
-    <t>1.36e+06</t>
-  </si>
-  <si>
-    <t>(62118.144)</t>
-  </si>
-  <si>
-    <t>3.297</t>
-  </si>
-  <si>
-    <t>(0.126)</t>
-  </si>
-  <si>
-    <t>6.122</t>
-  </si>
-  <si>
-    <t>(0.627)</t>
-  </si>
-  <si>
-    <t>44.082</t>
-  </si>
-  <si>
-    <t>(3.101)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.90e+05</t>
-  </si>
-  <si>
-    <t>-16.944</t>
-  </si>
-  <si>
-    <t>-0.286***</t>
-  </si>
-  <si>
-    <t>18.435***</t>
-  </si>
-  <si>
-    <t>3.590***</t>
-  </si>
-  <si>
-    <t>3.77e+05***</t>
-  </si>
-  <si>
-    <t>0.897***</t>
-  </si>
-  <si>
-    <t>3.212***</t>
-  </si>
-  <si>
-    <t>12.261**</t>
-  </si>
-  <si>
-    <t>0.060*</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>67</t>
+  </si>
+  <si>
+    <t>66</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.34e+05</t>
+  </si>
+  <si>
+    <t>(75084.004)</t>
+  </si>
+  <si>
+    <t>499.793</t>
+  </si>
+  <si>
+    <t>(36.056)</t>
+  </si>
+  <si>
+    <t>3.639</t>
+  </si>
+  <si>
+    <t>(0.050)</t>
+  </si>
+  <si>
+    <t>8.239</t>
+  </si>
+  <si>
+    <t>(1.393)</t>
+  </si>
+  <si>
+    <t>87.818</t>
+  </si>
+  <si>
+    <t>(0.501)</t>
+  </si>
+  <si>
+    <t>9.87e+05</t>
+  </si>
+  <si>
+    <t>(57883.460)</t>
+  </si>
+  <si>
+    <t>2.400</t>
+  </si>
+  <si>
+    <t>(0.140)</t>
+  </si>
+  <si>
+    <t>2.910</t>
+  </si>
+  <si>
+    <t>(0.408)</t>
+  </si>
+  <si>
+    <t>31.821</t>
+  </si>
+  <si>
+    <t>(3.927)</t>
+  </si>
+  <si>
+    <t>0.940</t>
+  </si>
+  <si>
+    <t>(0.029)</t>
+  </si>
+  <si>
+    <t>49</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.23e+05</t>
+  </si>
+  <si>
+    <t>(1.14e+05)</t>
+  </si>
+  <si>
+    <t>482.848</t>
+  </si>
+  <si>
+    <t>(48.706)</t>
+  </si>
+  <si>
+    <t>3.353</t>
+  </si>
+  <si>
+    <t>(0.051)</t>
+  </si>
+  <si>
+    <t>26.673</t>
+  </si>
+  <si>
+    <t>(3.766)</t>
+  </si>
+  <si>
+    <t>91.408</t>
+  </si>
+  <si>
+    <t>(0.410)</t>
+  </si>
+  <si>
+    <t>1.36e+06</t>
+  </si>
+  <si>
+    <t>(62118.144)</t>
+  </si>
+  <si>
+    <t>3.297</t>
+  </si>
+  <si>
+    <t>(0.126)</t>
+  </si>
+  <si>
+    <t>6.122</t>
+  </si>
+  <si>
+    <t>(0.627)</t>
+  </si>
+  <si>
+    <t>44.082</t>
+  </si>
+  <si>
+    <t>(3.101)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.90e+05</t>
+  </si>
+  <si>
+    <t>-16.944</t>
+  </si>
+  <si>
+    <t>-0.286***</t>
+  </si>
+  <si>
+    <t>18.435***</t>
+  </si>
+  <si>
+    <t>3.590***</t>
+  </si>
+  <si>
+    <t>3.77e+05***</t>
+  </si>
+  <si>
+    <t>0.897***</t>
+  </si>
+  <si>
+    <t>3.212***</t>
+  </si>
+  <si>
+    <t>12.261**</t>
+  </si>
+  <si>
+    <t>0.060*</t>
   </si>
 </sst>
 </file>
